--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_CRVENA ZVEZDA MERIDIANBET BELGRADE.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_CRVENA ZVEZDA MERIDIANBET BELGRADE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA40"/>
+  <dimension ref="A1:BA38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,13 +671,13 @@
         <v>0.2758620689655172</v>
       </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>13</v>
@@ -752,13 +752,13 @@
         <v>1.153846153846154</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.076923076923077</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
         <v>0.6428571428571429</v>
@@ -801,13 +801,13 @@
         <v>0.2758620689655172</v>
       </c>
       <c r="J3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>13</v>
@@ -882,13 +882,13 @@
         <v>1.153846153846154</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.076923076923077</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
         <v>0.6428571428571429</v>
@@ -931,13 +931,13 @@
         <v>0.1060606060606061</v>
       </c>
       <c r="J4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>8</v>
@@ -1012,13 +1012,13 @@
         <v>1.392857142857143</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
         <v>1.6</v>
@@ -1061,13 +1061,13 @@
         <v>0.1060606060606061</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>8</v>
@@ -1142,13 +1142,13 @@
         <v>1.392857142857143</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
         <v>1.6</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>49:53</t>
+          <t>29:51</t>
         </is>
       </c>
       <c r="AO8" t="n">
@@ -1575,13 +1575,13 @@
         <v>2.667</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.189</v>
+        <v>0.315</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.021</v>
+        <v>0.035</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.021</v>
+        <v>0.035</v>
       </c>
       <c r="BA8" t="n">
         <v>0.188</v>
@@ -1816,16 +1816,16 @@
         <v>12</v>
       </c>
       <c r="U10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>3</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>56:27</t>
+          <t>26:24</t>
         </is>
       </c>
       <c r="AO10" t="n">
@@ -1905,13 +1905,13 @@
         <v>16</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.132</v>
+        <v>0.281</v>
       </c>
       <c r="AY10" t="n">
         <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.056</v>
+        <v>0.12</v>
       </c>
       <c r="BA10" t="n">
         <v>0.125</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>35:19</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AO11" t="n">
@@ -2070,7 +2070,7 @@
         <v>6</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.194</v>
       </c>
       <c r="AY11" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>50:40</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AO12" t="n">
@@ -2235,13 +2235,13 @@
         <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.02</v>
+        <v>0.048</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.083</v>
+        <v>0.204</v>
       </c>
       <c r="BA12" t="n">
         <v>0</v>
@@ -2644,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>48:14</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AO15" t="n">
@@ -2730,13 +2730,13 @@
         <v>5</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.056</v>
+        <v>0.148</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.065</v>
+        <v>0.174</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.231</v>
       </c>
       <c r="BA15" t="n">
         <v>0.05</v>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AO16" t="n">
@@ -2895,13 +2895,13 @@
         <v>2</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.066</v>
+        <v>0.118</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.047</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.093</v>
+        <v>0.168</v>
       </c>
       <c r="BA16" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
         <v>10</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>34:35</t>
+          <t>24:35</t>
         </is>
       </c>
       <c r="AO17" t="n">
@@ -3060,13 +3060,13 @@
         <v>3</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.197</v>
+        <v>0.277</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.061</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.061</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="BA17" t="n">
         <v>0</v>
@@ -3139,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>40:42</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AO18" t="n">
@@ -3225,10 +3225,10 @@
         <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.081</v>
+        <v>0.159</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.103</v>
+        <v>0.204</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
@@ -3307,10 +3307,10 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>5</v>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>59:24</t>
+          <t>29:21</t>
         </is>
       </c>
       <c r="AO19" t="n">
@@ -3390,13 +3390,13 @@
         <v>5</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.144</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.035</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.089</v>
+        <v>0.179</v>
       </c>
       <c r="BA19" t="n">
         <v>0.043</v>
@@ -3570,65 +3570,65 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -3643,90 +3643,90 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>0.806</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>0.267</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>0.421</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:00</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>80.8</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>0.483</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>0.539</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>0.891</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>0.173</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>0.276</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>0.643</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>4.143</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>4.786</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>0.121</v>
       </c>
       <c r="BA21" t="n">
         <v>0</v>
@@ -3735,44 +3735,44 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D22" t="n">
+        <v>17</v>
+      </c>
+      <c r="E22" t="n">
+        <v>38</v>
+      </c>
+      <c r="F22" t="n">
         <v>13</v>
       </c>
-      <c r="E22" t="n">
-        <v>32</v>
-      </c>
-      <c r="F22" t="n">
-        <v>10</v>
-      </c>
       <c r="G22" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H22" t="n">
+        <v>7</v>
+      </c>
+      <c r="I22" t="n">
+        <v>14</v>
+      </c>
+      <c r="J22" t="n">
         <v>16</v>
       </c>
-      <c r="I22" t="n">
-        <v>20</v>
-      </c>
-      <c r="J22" t="n">
-        <v>9</v>
-      </c>
       <c r="K22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N22" t="n">
         <v>4</v>
@@ -3781,76 +3781,76 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q22" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S22" t="n">
         <v>21</v>
       </c>
       <c r="T22" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="U22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
         <v>14</v>
       </c>
-      <c r="W22" t="n">
-        <v>4</v>
-      </c>
-      <c r="X22" t="n">
+      <c r="Z22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
         <v>3</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AL22" t="n">
         <v>25</v>
       </c>
-      <c r="Z22" t="n">
-        <v>31</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.806</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>19</v>
-      </c>
       <c r="AM22" t="n">
-        <v>0.421</v>
+        <v>0.52</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
@@ -3858,40 +3858,40 @@
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>80.8</v>
+        <v>82.16</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.483</v>
+        <v>0.553</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.539</v>
+        <v>0.554</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.891</v>
+        <v>0.974</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.173</v>
+        <v>0.122</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.276</v>
+        <v>0.106</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.643</v>
+        <v>1.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.143</v>
+        <v>6.6</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.786</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX22" t="n">
         <v>0.2</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.068</v>
+        <v>0.079</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.121</v>
+        <v>0.132</v>
       </c>
       <c r="BA22" t="n">
         <v>0</v>
@@ -3900,250 +3900,250 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="n">
-        <v>80</v>
-      </c>
-      <c r="D23" t="n">
-        <v>17</v>
-      </c>
-      <c r="E23" t="n">
-        <v>38</v>
-      </c>
-      <c r="F23" t="n">
-        <v>13</v>
-      </c>
-      <c r="G23" t="n">
-        <v>28</v>
-      </c>
-      <c r="H23" t="n">
-        <v>7</v>
-      </c>
-      <c r="I23" t="n">
-        <v>14</v>
-      </c>
-      <c r="J23" t="n">
-        <v>16</v>
-      </c>
-      <c r="K23" t="n">
-        <v>25</v>
-      </c>
-      <c r="L23" t="n">
-        <v>15</v>
-      </c>
-      <c r="M23" t="n">
-        <v>8</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>8</v>
-      </c>
-      <c r="R23" t="n">
-        <v>21</v>
-      </c>
-      <c r="S23" t="n">
-        <v>21</v>
-      </c>
-      <c r="T23" t="n">
-        <v>95</v>
-      </c>
-      <c r="U23" t="n">
-        <v>7</v>
-      </c>
-      <c r="V23" t="n">
-        <v>15</v>
-      </c>
-      <c r="W23" t="n">
-        <v>5</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO23" t="n">
-        <v>82.16</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0.553</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0.554</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0.974</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="inlineStr"/>
-      <c r="AQ24" t="inlineStr"/>
-      <c r="AR24" t="inlineStr"/>
-      <c r="AS24" t="inlineStr"/>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AU24" t="inlineStr"/>
-      <c r="AV24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr"/>
-      <c r="AX24" t="inlineStr"/>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr"/>
-      <c r="BA24" t="inlineStr"/>
+          <t>#0 C. MILLER-MCINTYRE (Per Game)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>19</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>9</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>6</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>13</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>29:51</t>
+        </is>
+      </c>
+      <c r="AO24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0.188</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>#0 C. MILLER-MCINTYRE (Per Game)</t>
+          <t>#2 S. MILJENOVIC (Per Game)</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -4152,43 +4152,43 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -4197,118 +4197,118 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>49:53</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.731</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.731</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.316</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.167</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.667</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.189</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>0.188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>#2 S. MILJENOVIC (Per Game)</t>
+          <t>#6 J. BUTLER (Per Game)</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -4317,16 +4317,16 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -4335,19 +4335,19 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -4362,22 +4362,22 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4392,88 +4392,88 @@
         <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ26" t="n">
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>26:24</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.067</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>0.281</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>#6 J. BUTLER (Per Game)</t>
+          <t>#11 T. CARTER (Per Game)</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -4482,67 +4482,67 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
         <v>3</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" t="n">
-        <v>3</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
       <c r="T27" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -4557,88 +4557,88 @@
         <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AM27" t="n">
         <v>0.5</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>56:27</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.571</v>
+        <v>0.3</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.571</v>
+        <v>0.3</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.067</v>
+        <v>0.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.067</v>
+        <v>0.167</v>
       </c>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV27" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AW27" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.132</v>
+        <v>0.194</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.056</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.125</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>#11 T. CARTER (Per Game)</t>
+          <t>#12 N. KALINIC (Per Game)</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -4647,10 +4647,10 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -4665,19 +4665,19 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -4695,7 +4695,7 @@
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4704,7 +4704,7 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -4722,69 +4722,69 @@
         <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ28" t="n">
         <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>35:19</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.048</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>0.204</v>
       </c>
       <c r="BA28" t="n">
-        <v>0.045</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>#12 N. KALINIC (Per Game)</t>
+          <t>#13 O. DOBRIC (Per Game)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -4797,13 +4797,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -4815,7 +4815,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -4836,13 +4836,13 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -4878,7 +4878,7 @@
         <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -4887,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
         <v>0</v>
@@ -4903,11 +4903,11 @@
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>50:40</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP29" t="n">
         <v>0</v>
@@ -4934,13 +4934,13 @@
         <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
         <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
         <v>0</v>
@@ -4949,20 +4949,20 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>#13 O. DOBRIC (Per Game)</t>
+          <t>#14 J. RIVERO (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -4974,7 +4974,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -5001,13 +5001,13 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -5022,13 +5022,13 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -5068,20 +5068,20 @@
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:27</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>0.694</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.389</v>
       </c>
       <c r="AS30" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>0.291</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
@@ -5114,20 +5114,20 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#14 J. RIVERO (Per Game)</t>
+          <t>#15 E. IZUNDU (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -5136,43 +5136,43 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -5187,13 +5187,13 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA31" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -5233,243 +5233,243 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>02:27</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>1.44</v>
+        <v>5.44</v>
       </c>
       <c r="AP31" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.694</v>
+        <v>0.788</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.389</v>
+        <v>1.287</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>0.184</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.291</v>
+        <v>0.148</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>0.174</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#15 E. IZUNDU (Per Game)</t>
+          <t>#21 J. BOLOMBOY (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AO32" t="n">
         <v>3</v>
       </c>
-      <c r="E32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>4</v>
-      </c>
-      <c r="L32" t="n">
-        <v>3</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>3</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>15</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>5</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>48:14</t>
-        </is>
-      </c>
-      <c r="AO32" t="n">
-        <v>5.44</v>
-      </c>
       <c r="AP32" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.788</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.287</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.184</v>
+        <v>0.333</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.056</v>
+        <v>0.118</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.065</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.168</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#21 J. BOLOMBOY (Per Game)</t>
+          <t>#33 J. NWORA (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -5478,7 +5478,7 @@
         <v>2</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -5490,19 +5490,19 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -5517,22 +5517,22 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -5547,60 +5547,60 @@
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ33" t="n">
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>24:35</t>
         </is>
       </c>
       <c r="AO33" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
         <v>3</v>
       </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>2</v>
-      </c>
       <c r="AW33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.066</v>
+        <v>0.277</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.047</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.093</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="BA33" t="n">
         <v>0</v>
@@ -5609,68 +5609,68 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#33 J. NWORA (Per Game)</t>
+          <t>#37 S. OJELEYE (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3</v>
+      </c>
+      <c r="H34" t="n">
+        <v>6</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="n">
-        <v>5</v>
-      </c>
-      <c r="H34" t="n">
-        <v>4</v>
-      </c>
-      <c r="I34" t="n">
-        <v>4</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2</v>
-      </c>
-      <c r="L34" t="n">
-        <v>2</v>
-      </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -5682,22 +5682,22 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z34" t="n">
         <v>6</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -5709,136 +5709,136 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>2</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>34:35</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>13.76</v>
+        <v>6.64</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.389</v>
+        <v>0.375</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.511</v>
+        <v>0.678</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.799</v>
+        <v>1.355</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.218</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.444</v>
+        <v>1.5</v>
       </c>
       <c r="AU34" t="n">
         <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.197</v>
+        <v>0.159</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.061</v>
+        <v>0.204</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#37 S. OJELEYE (Per Game)</t>
+          <t>#95 C. MONEKE (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I35" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L35" t="n">
+        <v>2</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="n">
         <v>4</v>
       </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>2</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3</v>
-      </c>
       <c r="T35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -5847,19 +5847,19 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z35" t="n">
         <v>6</v>
       </c>
       <c r="AA35" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5874,109 +5874,109 @@
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
         <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM35" t="n">
         <v>0</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>40:42</t>
+          <t>29:21</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>6.64</v>
+        <v>8.52</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.678</v>
+        <v>0.332</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.355</v>
+        <v>0.587</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>0.117</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.081</v>
+        <v>0.144</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.103</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.045</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#95 C. MONEKE (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -5985,19 +5985,19 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -6006,25 +6006,25 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.833</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -6051,118 +6051,118 @@
         <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
         <v>0</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>59:24</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>8.52</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
         <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.332</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.587</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.117</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -6177,90 +6177,90 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>0.806</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>0.267</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>0.421</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:00</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>80.8</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>0.483</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>0.539</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>0.891</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>0.173</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>0.276</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>0.643</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>4.143</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>4.786</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>0.121</v>
       </c>
       <c r="BA37" t="n">
         <v>0</v>
@@ -6269,65 +6269,65 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="T38" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -6342,28 +6342,28 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>0.636</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>0.476</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -6372,392 +6372,62 @@
         <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ38" t="n">
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:00</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>82.16</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>0.553</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>0.554</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>0.974</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>0.122</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>0.106</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>0.203</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>0.079</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>0.132</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" t="n">
-        <v>72</v>
-      </c>
-      <c r="D39" t="n">
-        <v>13</v>
-      </c>
-      <c r="E39" t="n">
-        <v>32</v>
-      </c>
-      <c r="F39" t="n">
-        <v>10</v>
-      </c>
-      <c r="G39" t="n">
-        <v>26</v>
-      </c>
-      <c r="H39" t="n">
-        <v>16</v>
-      </c>
-      <c r="I39" t="n">
-        <v>20</v>
-      </c>
-      <c r="J39" t="n">
-        <v>9</v>
-      </c>
-      <c r="K39" t="n">
-        <v>23</v>
-      </c>
-      <c r="L39" t="n">
-        <v>13</v>
-      </c>
-      <c r="M39" t="n">
-        <v>4</v>
-      </c>
-      <c r="N39" t="n">
-        <v>4</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>13</v>
-      </c>
-      <c r="R39" t="n">
-        <v>20</v>
-      </c>
-      <c r="S39" t="n">
-        <v>21</v>
-      </c>
-      <c r="T39" t="n">
-        <v>73</v>
-      </c>
-      <c r="U39" t="n">
-        <v>7</v>
-      </c>
-      <c r="V39" t="n">
-        <v>14</v>
-      </c>
-      <c r="W39" t="n">
-        <v>4</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>31</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0.806</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>8</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>19</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO39" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0.483</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0.539</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>0.891</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>0.173</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>4.143</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>4.786</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="n">
-        <v>80</v>
-      </c>
-      <c r="D40" t="n">
-        <v>17</v>
-      </c>
-      <c r="E40" t="n">
-        <v>38</v>
-      </c>
-      <c r="F40" t="n">
-        <v>13</v>
-      </c>
-      <c r="G40" t="n">
-        <v>28</v>
-      </c>
-      <c r="H40" t="n">
-        <v>7</v>
-      </c>
-      <c r="I40" t="n">
-        <v>14</v>
-      </c>
-      <c r="J40" t="n">
-        <v>16</v>
-      </c>
-      <c r="K40" t="n">
-        <v>25</v>
-      </c>
-      <c r="L40" t="n">
-        <v>15</v>
-      </c>
-      <c r="M40" t="n">
-        <v>8</v>
-      </c>
-      <c r="N40" t="n">
-        <v>4</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>8</v>
-      </c>
-      <c r="R40" t="n">
-        <v>21</v>
-      </c>
-      <c r="S40" t="n">
-        <v>21</v>
-      </c>
-      <c r="T40" t="n">
-        <v>95</v>
-      </c>
-      <c r="U40" t="n">
-        <v>7</v>
-      </c>
-      <c r="V40" t="n">
-        <v>15</v>
-      </c>
-      <c r="W40" t="n">
-        <v>5</v>
-      </c>
-      <c r="X40" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>13</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO40" t="n">
-        <v>82.16</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0.553</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0.554</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0.974</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>0.203</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="BA40" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_CRVENA ZVEZDA MERIDIANBET BELGRADE.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_CRVENA ZVEZDA MERIDIANBET BELGRADE.xlsx
@@ -671,13 +671,13 @@
         <v>0.2758620689655172</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
         <v>13</v>
@@ -752,13 +752,13 @@
         <v>1.153846153846154</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN2" t="n">
         <v>0.6428571428571429</v>
@@ -801,13 +801,13 @@
         <v>0.2758620689655172</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
         <v>13</v>
@@ -882,13 +882,13 @@
         <v>1.153846153846154</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN3" t="n">
         <v>0.6428571428571429</v>
@@ -931,13 +931,13 @@
         <v>0.1060606060606061</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
         <v>8</v>
@@ -1012,13 +1012,13 @@
         <v>1.392857142857143</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AN4" t="n">
         <v>1.6</v>
@@ -1061,13 +1061,13 @@
         <v>0.1060606060606061</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
         <v>8</v>
@@ -1142,13 +1142,13 @@
         <v>1.392857142857143</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AN5" t="n">
         <v>1.6</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1816,16 +1816,16 @@
         <v>12</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
         <v>3</v>
@@ -2644,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
         <v>10</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3139,13 +3139,13 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="n">
         <v>6</v>
@@ -3307,10 +3307,10 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
         <v>5</v>
@@ -3631,16 +3631,16 @@
         <v>73</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y21" t="n">
         <v>25</v>
@@ -3796,16 +3796,16 @@
         <v>95</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="n">
         <v>14</v>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -4350,16 +4350,16 @@
         <v>12</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
         <v>3</v>
@@ -5178,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>10</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -5673,13 +5673,13 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y34" t="n">
         <v>6</v>
@@ -5841,10 +5841,10 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
         <v>5</v>
@@ -6165,16 +6165,16 @@
         <v>73</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y37" t="n">
         <v>25</v>
@@ -6330,16 +6330,16 @@
         <v>95</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y38" t="n">
         <v>14</v>

--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_CRVENA ZVEZDA MERIDIANBET BELGRADE.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_CRVENA ZVEZDA MERIDIANBET BELGRADE.xlsx
@@ -683,13 +683,13 @@
         <v>13</v>
       </c>
       <c r="N2" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="O2" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5344827586206896</v>
+        <v>0.2586206896551724</v>
       </c>
       <c r="Q2" t="n">
         <v>4</v>
@@ -710,25 +710,25 @@
         <v>0.03448275862068965</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.1724137931034483</v>
+      </c>
+      <c r="Z2" t="n">
         <v>7</v>
       </c>
-      <c r="Y2" t="n">
-        <v>0.1206896551724138</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>8</v>
-      </c>
       <c r="AA2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3275862068965517</v>
+        <v>0.2758620689655172</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8064516129032258</v>
+        <v>0.6</v>
       </c>
       <c r="AD2" t="n">
         <v>0.2666666666666667</v>
@@ -737,13 +737,13 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.4375</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.612903225806452</v>
+        <v>1.2</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -813,13 +813,13 @@
         <v>13</v>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5344827586206896</v>
+        <v>0.2586206896551724</v>
       </c>
       <c r="Q3" t="n">
         <v>4</v>
@@ -840,25 +840,25 @@
         <v>0.03448275862068965</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.1724137931034483</v>
+      </c>
+      <c r="Z3" t="n">
         <v>7</v>
       </c>
-      <c r="Y3" t="n">
-        <v>0.1206896551724138</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>8</v>
-      </c>
       <c r="AA3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3275862068965517</v>
+        <v>0.2758620689655172</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8064516129032258</v>
+        <v>0.6</v>
       </c>
       <c r="AD3" t="n">
         <v>0.2666666666666667</v>
@@ -867,13 +867,13 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.4375</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.612903225806452</v>
+        <v>1.2</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -943,13 +943,13 @@
         <v>8</v>
       </c>
       <c r="N4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="Q4" t="n">
         <v>10</v>
@@ -988,7 +988,7 @@
         <v>0.3787878787878788</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="AD4" t="n">
         <v>0.4761904761904762</v>
@@ -1003,7 +1003,7 @@
         <v>0.52</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.272727272727273</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1073,13 +1073,13 @@
         <v>8</v>
       </c>
       <c r="N5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="Q5" t="n">
         <v>10</v>
@@ -1118,7 +1118,7 @@
         <v>0.3787878787878788</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="AD5" t="n">
         <v>0.4761904761904762</v>
@@ -1133,7 +1133,7 @@
         <v>0.52</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.272727272727273</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -2020,22 +2020,22 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
@@ -2653,13 +2653,13 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z15" t="n">
         <v>4</v>
       </c>
-      <c r="Z15" t="n">
-        <v>5</v>
-      </c>
       <c r="AA15" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2983,13 +2983,13 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.833</v>
+        <v>0.5</v>
       </c>
       <c r="AB17" t="n">
         <v>1</v>
@@ -3148,13 +3148,13 @@
         <v>2</v>
       </c>
       <c r="Y18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -3178,16 +3178,16 @@
         <v>1</v>
       </c>
       <c r="AI18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
@@ -3313,13 +3313,13 @@
         <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.833</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -3643,13 +3643,13 @@
         <v>4</v>
       </c>
       <c r="Y21" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="Z21" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.806</v>
+        <v>0.6</v>
       </c>
       <c r="AB21" t="n">
         <v>4</v>
@@ -3670,22 +3670,22 @@
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AK21" t="n">
         <v>7</v>
       </c>
-      <c r="AJ21" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>8</v>
-      </c>
       <c r="AL21" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.421</v>
+        <v>0.438</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
@@ -3808,13 +3808,13 @@
         <v>2</v>
       </c>
       <c r="Y22" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Z22" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.636</v>
+        <v>0.467</v>
       </c>
       <c r="AB22" t="n">
         <v>10</v>
@@ -4554,22 +4554,22 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
@@ -5187,13 +5187,13 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z31" t="n">
         <v>4</v>
       </c>
-      <c r="Z31" t="n">
-        <v>5</v>
-      </c>
       <c r="AA31" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -5517,13 +5517,13 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z33" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.833</v>
+        <v>0.5</v>
       </c>
       <c r="AB33" t="n">
         <v>1</v>
@@ -5682,13 +5682,13 @@
         <v>2</v>
       </c>
       <c r="Y34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -5712,16 +5712,16 @@
         <v>1</v>
       </c>
       <c r="AI34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="AK34" t="n">
         <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
         <v>0</v>
@@ -5847,13 +5847,13 @@
         <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.833</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         <v>4</v>
       </c>
       <c r="Y37" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="Z37" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.806</v>
+        <v>0.6</v>
       </c>
       <c r="AB37" t="n">
         <v>4</v>
@@ -6204,22 +6204,22 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI37" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AK37" t="n">
         <v>7</v>
       </c>
-      <c r="AJ37" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>8</v>
-      </c>
       <c r="AL37" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.421</v>
+        <v>0.438</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
@@ -6342,13 +6342,13 @@
         <v>2</v>
       </c>
       <c r="Y38" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Z38" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.636</v>
+        <v>0.467</v>
       </c>
       <c r="AB38" t="n">
         <v>10</v>
